--- a/pdf2img/tabel/table_7.xlsx
+++ b/pdf2img/tabel/table_7.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,21 @@
       </c>
       <c r="P1" t="n">
         <v>15</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="2">
@@ -511,15 +526,28 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Per,3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>[Per;31[Desember</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dan"2024</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -533,21 +561,38 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1|Desember;2025</t>
+          <t>{</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dan'2024</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jutaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rupiah</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -559,33 +604,22 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dafam</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>jutaan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>rupiah</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>)</t>
-        </is>
-      </c>
+          <t>“_31-095-24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -597,98 +631,213 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>POS-POS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8Des-25</t>
+          <t>|</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ckpN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>s—‘(‘i—‘“‘“&lt;idrts</t>
+          <t>|</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Des</t>
+          <t>PPKAwajibdibentuk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ssi</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cKPN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PPKAwajib</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dibentuk</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stage1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stage2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stage3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Umum</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Khusus</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Stage1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Stage2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stage3</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Umum</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Khusus</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Po</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CCKPNC—C—C—C—C‘*dCL:*SCsPPKAwwajibb</t>
+          <t>Penempatan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>pada</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CCKPNS</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CdS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>lain</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14.108</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -699,31 +848,36 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POS-POS</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ibentuk</t>
+          <t>Tagihan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PPKA</t>
+          <t>spof</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wajib</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dibentuk</t>
+          <t>derivatif/forward</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -737,176 +891,200 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>berharga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[|</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Umum</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Khusus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Stage1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Stage2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Umum</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
+          <t>dimiliki</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stagei</t>
+          <t>4.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stage2</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Khusus</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{Repo)</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stage3_</t>
+          <t>5.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stage3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Tagihan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>atas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>surat</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>6.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Penempatan</t>
+          <t>Tagihan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>14.109</t>
-        </is>
-      </c>
+          <t>akseptasi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -917,36 +1095,53 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>7.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tagihan</t>
+          <t>Kredit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>diberikan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>dan</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>derivatif/forward</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pembiayaan</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>diberikan</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -955,28 +1150,29 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Penyertaan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>berharga</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>dimiliki</t>
-        </is>
-      </c>
+          <t>modal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -989,15 +1185,28 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tagihan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1011,53 +1220,26 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>berharga</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>dijual</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>janji</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>dibeli</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>(Repo)</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1065,16 +1247,33 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>|Komitmen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>kontinjensi</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1087,286 +1286,11 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Tagihan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>atas</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>surat</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>berharga</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>dibeli</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>janji</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dijual</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Tagihan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>akseptasi</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Kredit</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>diberikan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>pembiayaan</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>diberikan</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>130.201</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Penyertaan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>modal</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>9.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tagihan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>lainnya</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>|Komitmen</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>kontinjensi</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
